--- a/docs/design/04_データ設計書_HackerLake.xlsx
+++ b/docs/design/04_データ設計書_HackerLake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phrx4\hackerlake\docs\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0946316-2DD5-45C1-8629-0B60CFE4E840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{089F6153-F2B0-4769-A313-27D1F1C4CF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{A3CD5EA5-EB42-4D20-A445-4EA4D3DFAC52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{18BAF2E9-F083-4F3E-9FB8-8C93163AA66E}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,18 @@
     <sheet name="エッジ定義" sheetId="4" r:id="rId4"/>
     <sheet name="将来物理設計" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Webノード初期定義!$A$3:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">エッジ定義!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">データモデル一覧!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">将来物理設計!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">表紙!$A$3:$H$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Webノード初期定義!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">エッジ定義!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">データモデル一覧!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">将来物理設計!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">表紙!$1:$3</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -617,7 +629,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -644,15 +656,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -668,6 +686,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF006080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,7 +725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -709,12 +733,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1030,18 +1057,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95EFFAAF-1397-4CC3-8783-0B1C83245C0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B142D72C-061D-4B3D-B885-F5671D491D39}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1084,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1079,7 +1110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1097,33 +1128,33 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>46186</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1150,27 +1181,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H6" xr:uid="{B142D72C-061D-4B3D-B885-F5671D491D39}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D7D469-F28F-436D-9AC9-139A978233A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E102A1-9FAD-4B9E-9F88-9474DD7CB178}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1182,7 +1219,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -1208,7 +1245,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -1234,33 +1271,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>51</v>
       </c>
@@ -1286,33 +1323,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>64</v>
       </c>
@@ -1338,54 +1375,60 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H9" xr:uid="{C0E102A1-9FAD-4B9E-9F88-9474DD7CB178}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FC7C5F-D4FD-4397-A48A-3BA2E3CD0BF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF382B3-745B-4BEE-9538-1ADF3765626D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
@@ -1397,7 +1440,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>80</v>
       </c>
@@ -1423,7 +1466,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="49.5">
       <c r="A4" s="3" t="s">
         <v>85</v>
       </c>
@@ -1449,33 +1492,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>98</v>
       </c>
@@ -1501,33 +1544,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>110</v>
       </c>
@@ -1553,33 +1596,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>121</v>
       </c>
@@ -1605,54 +1648,60 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H11" xr:uid="{8DF382B3-745B-4BEE-9538-1ADF3765626D}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F150EC8-0C82-4535-B07C-58E009A33638}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DB987C-2DD9-4E31-83F0-30AAD1345EAA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
@@ -1664,7 +1713,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>134</v>
       </c>
@@ -1690,7 +1739,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>141</v>
       </c>
@@ -1714,31 +1763,31 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>147</v>
       </c>
@@ -1762,31 +1811,31 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>154</v>
       </c>
@@ -1810,31 +1859,31 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>160</v>
       </c>
@@ -1859,27 +1908,33 @@
       <c r="H10" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H10" xr:uid="{23DB987C-2DD9-4E31-83F0-30AAD1345EAA}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2414219D-EAB9-4D5F-B19C-9311061E94B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AE9152-8026-4E71-BB46-8FCC283FFA41}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>164</v>
       </c>
@@ -1891,7 +1946,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>165</v>
       </c>
@@ -1917,7 +1972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>170</v>
       </c>
@@ -1943,33 +1998,33 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>181</v>
       </c>
@@ -1995,33 +2050,33 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>190</v>
       </c>
@@ -2048,10 +2103,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{58AE9152-8026-4E71-BB46-8FCC283FFA41}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>